--- a/CUSTOMERS_from_BC.xlsx
+++ b/CUSTOMERS_from_BC.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="CUSTOMERS" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="BC_CUSTOMERS" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="READ ME FIRST" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="357">
   <si>
     <t xml:space="preserve">Company Name</t>
   </si>
@@ -1119,7 +1119,10 @@
     <t xml:space="preserve">1. Skim the yellow rows using column D's explanation — change column B via its dropdown if a different area is more accurate.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Copy columns A and B (Company Name, Delivery Area) and paste them into the "CUSTOMERS" tab of your order system's Google Sheet, starting at cell A2.</t>
+    <t xml:space="preserve">2. Copy columns A and B (Company Name, Delivery Area) and paste them into the "BC_CUSTOMERS" tab of your order system's Google Sheet, starting at cell A2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Important: this is a tab called BC_CUSTOMERS, deliberately separate from any "CUSTOMERS" tab you may already use for your WhatsApp leads or general contact list. Never paste this into that tab — the order system only ever reads BC_CUSTOMERS, and mixing the two would mean leads that never ordered end up looking like real, address-matched customers.</t>
   </si>
   <si>
     <t xml:space="preserve">3. Columns C, D, E, F and G are just for your reference — the order form never reads them, so it's fine to leave them out of what you paste.</t>
@@ -4094,7 +4097,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="105"/>
@@ -4154,6 +4157,11 @@
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
         <v>355</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>
